--- a/VerveStacks_KEN_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_KEN_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20B30D4C-4918-4310-AA8D-694887612080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55B3A20C-102C-4797-B9B3-3BDAA7C048F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -639,10 +639,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>RaD,RaP,FaD,SaD,FaP,SaP,WaD,WaP</t>
-  </si>
-  <si>
-    <t>WaP,RaP,FaP,SaP,SaN,WaN,FaN,RaN</t>
+    <t>FaD,WaP,RaP,RaD,SaD,FaP,SaP,WaD</t>
+  </si>
+  <si>
+    <t>SaN,WaN,FaN,RaP,RaN,FaP,SaP,WaP</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>WaP,RaP,FaP,SaP,SaN,WaN,FaN,RaN</v>
+        <v>SaN,WaN,FaN,RaP,RaN,FaP,SaP,WaP</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>RaD,RaP,FaD,SaD,FaP,SaP,WaD,WaP</v>
+        <v>FaD,WaP,RaP,RaD,SaD,FaP,SaP,WaD</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1365,7 +1365,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62AF40DF-D3DC-426F-83CC-3A8B13951C93}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BFEE72-2E19-49F8-9BF5-870B7CE37F6D}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1449,7 +1449,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43119B2F-F20D-434D-BD3D-D1C5D6F603BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1063982-E8FB-47B4-8915-78628301FDDA}">
   <dimension ref="B9:O346"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10967,7 +10967,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{232DEC4D-1FF3-4236-8FC1-BC488BA8D611}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D844DA56-0EE6-4AA1-B675-9EC21A683C2F}">
   <dimension ref="B9:BL71"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17225,7 +17225,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B45F367-EE7A-40DA-9D3C-5B1F204D9A43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5EDE66D-BAE8-4484-B401-FEF2B75BB944}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17423,7 +17423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9558BC09-A218-4D2A-BDEA-3F8BB06EE010}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BED0DC48-5B99-4CF3-A37B-843221C14F80}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17714,7 +17714,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2D1F349-9F7F-460B-9F9E-87FBE5A58D28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBDA94AE-1048-4F71-8873-25BD328D6DAA}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17873,7 +17873,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998B41EA-E941-44BA-B0FC-F097DA3D82DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4F5185E-E940-4550-9FFD-668A869E4844}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17919,7 +17919,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.52183333333333337</v>
+        <v>0.52183333333333326</v>
       </c>
       <c r="E12" t="s">
         <v>206</v>
@@ -18143,7 +18143,7 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>0.37329999999999997</v>
+        <v>0.37330000000000002</v>
       </c>
       <c r="E28" t="s">
         <v>206</v>
@@ -18311,7 +18311,7 @@
         <v>41</v>
       </c>
       <c r="D40">
-        <v>0.35450000000000004</v>
+        <v>0.35449999999999998</v>
       </c>
       <c r="E40" t="s">
         <v>206</v>
@@ -18423,7 +18423,7 @@
         <v>41</v>
       </c>
       <c r="D48">
-        <v>0.46609999999999996</v>
+        <v>0.46610000000000001</v>
       </c>
       <c r="E48" t="s">
         <v>206</v>
